--- a/expert-system/output/security/security.xlsx
+++ b/expert-system/output/security/security.xlsx
@@ -18,6 +18,7 @@
     <sheet name="TS-SEC-InfoLeak" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-SEC-ObjPerm" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="TS-SEC-InputVal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Test Data" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Risk Assessment'!$A$4:$F$17</definedName>
@@ -37,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +90,12 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -145,6 +150,12 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -172,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,6 +219,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -876,6 +897,13 @@
       </c>
       <c r="D23" s="11" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Test Data Reference</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId1"/>
@@ -886,6 +914,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2249,6 +2278,754 @@
   <autoFilter ref="A3:J16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Security Module Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>1. Recommended Test Users (Module-Specific)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>User / Query</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Use perekrest</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>7 roles</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Maximum privilege — JWT contains all authorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Use alsmirnov</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>EMPLOYEE only</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Minimum privilege baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Use any contractor</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>CONTRACTOR</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Special permissions: cannot create vacations</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>2. Common Multi-Role Test Users (All Modules)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Best For</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>perekrest</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_ACCOUNTANT, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Best multi-role user (7 roles). Use for cross-role permission testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>pvaynmaster</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_OFFICER, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Multi-role with CHIEF_OFFICER. Use for highest-privilege scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ilnitsky</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Admin+accountant combo. Use for accounting and admin tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Same role set as ilnitsky. Use as second admin/accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, HR, PM, VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Has VIEW_ALL. Use for read-only permission tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>kcherenkov</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, PM, TECH_LEAD</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tech Lead + PM. Use for planner/project management tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>alsmirnov</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>EMPLOYEE-only. Use as minimum-privilege baseline user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>3. Common SQL Queries (User Discovery)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Find EMPLOYEE-only users (minimum privilege)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.id
+HAVING COUNT(*) = 1 AND MAX(r.role) = 'ROLE_EMPLOYEE'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Find active contractors</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_CONTRACTOR'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Find active project managers</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_PROJECT_MANAGER'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Find active accountants</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ACCOUNTANT'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Find active admins</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ADMIN'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Get current report/approve periods per office</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name,
+       rp.start as report_period_start,
+       ap.start as approve_period_start
+FROM office o
+JOIN office_period rp ON o.report_period_id = rp.id
+JOIN office_period ap ON o.approve_period_id = ap.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>ttt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>4. Module-Specific SQL Queries</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Find users by role count (for authorization boundary tests)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, COUNT(r.role) as role_count,
+       STRING_AGG(r.role, ', ') as roles
+FROM ttt_backend.employee e
+JOIN ttt_backend.employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.login
+ORDER BY role_count DESC LIMIT 15;</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Find endpoints missing @PreAuthorize (code-level)</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>-- Grep codebase for controllers without @PreAuthorize:
+-- grep -rn '@RestController' --include='*.java' | \
+--   xargs -I{} grep -L '@PreAuthorize' {}
+-- Known gaps: EmployeeController in admin module</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Find API token configuration</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>-- API token is configured in application properties:
+-- ttt.api.secret.token=&lt;value&gt;
+-- Header: API_SECRET_TOKEN
+-- Grants ROLE_API_USER scope (limited endpoints)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Active session check</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>-- JWT tokens are stateless (no server-side session table)
+-- Token expiry: check 'exp' claim in decoded JWT
+-- Decode: echo '&lt;jwt_token&gt;' | cut -d. -f2 | base64 -d | jq .</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>5. Data Generation Strategies</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>JWT token extraction</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO. Extract TTT_JWT_TOKEN cookie from browser dev tools or Playwright. Decode with base64.</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN with value from env config. Test both valid and invalid/expired tokens.</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Permission boundary</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>For each endpoint: test as authorized role (expect 200), test as unauthorized role (expect 403), test as unauthenticated (expect 401).</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>IDOR testing</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Replace {id} in URL with another user's resource ID. Expect 403 or filtered response (not 200 with other user's data).</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>6. Environment Reference</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>timemachine</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>https://ttt-timemachine.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Primary dev env — has test clock (PATCH to advance time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>qa-1</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>https://ttt-qa-1.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Secondary dev env — real clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>https://ttt-stage.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Production-like env — read-only testing preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>7. API Authentication</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>How to Obtain/Use</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>JWT (user context)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO at /login, extract TTT_JWT_TOKEN cookie. Pass as Authorization: Bearer &lt;token&gt; or Cookie header.</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Most endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN: &lt;token_value&gt;. Value from env config file.</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Test/sync endpoints, limited scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
